--- a/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>162 LOS HONGUITOS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-3.74757</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.25349</v>
-      </c>
-      <c r="I2" t="n">
-        <v>678</v>
-      </c>
-      <c r="J2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.74757</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.25349</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>172 ANGEL DE LA GUARDA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-3.7415</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.257693</v>
-      </c>
-      <c r="I3" t="n">
-        <v>357</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-3.7415</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.257693</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>179 EL PILOTO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-3.75457</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.25263</v>
-      </c>
-      <c r="I4" t="n">
-        <v>231</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3.75457</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.25263</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>312 GRILLITO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-3.74532</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.26427</v>
-      </c>
-      <c r="I5" t="n">
-        <v>300</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-3.74532</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.26427</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>313</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-3.73593</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.24925</v>
-      </c>
-      <c r="I6" t="n">
-        <v>351</v>
-      </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.73593</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.24925</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>330</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-3.805688</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.34148</v>
-      </c>
-      <c r="I7" t="n">
-        <v>246</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-3.805688</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.34148</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>342</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-3.75575</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.27121</v>
-      </c>
-      <c r="I8" t="n">
-        <v>449</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-3.75575</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.27121</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>476 LOS ARBOLITOS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-3.74002</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.24925</v>
-      </c>
-      <c r="I9" t="n">
-        <v>264</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-3.74002</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.24925</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>593 MIS GARABATOS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-3.73247</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.26884</v>
-      </c>
-      <c r="I10" t="n">
-        <v>202</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-3.73247</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.26884</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>691 RAYITOS DE ESPERANZA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-3.72995</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.2625</v>
-      </c>
-      <c r="I11" t="n">
-        <v>308</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-3.72995</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.2625</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>717</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-3.7512</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.25926</v>
-      </c>
-      <c r="I12" t="n">
-        <v>346</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-3.7512</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.25926</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>601374 SIMON BOLIVAR / 754</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-3.777049</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.302092</v>
-      </c>
-      <c r="I13" t="n">
-        <v>482</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-3.777049</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.302092</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>60756 CLAVERITO / 756 CLAVERITO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-3.7327</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.24986</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1814</v>
-      </c>
-      <c r="J14" t="n">
-        <v>82</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-3.7327</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.24986</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>60001 MENELEO MEZA LOPEZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-3.75599</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.24995</v>
-      </c>
-      <c r="I15" t="n">
-        <v>282</v>
-      </c>
-      <c r="J15" t="n">
-        <v>16</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-3.75599</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.24995</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>60002 ANTONIO ALVAREZ VASQUEZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-3.756</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.25328399999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>228</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-3.756</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.253284</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>60005 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-3.76083</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.25421</v>
-      </c>
-      <c r="I17" t="n">
-        <v>869</v>
-      </c>
-      <c r="J17" t="n">
-        <v>52</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.76083</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.25421</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>60007 BRASIL</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-3.74889</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-73.25398</v>
-      </c>
-      <c r="I18" t="n">
-        <v>213</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.74889</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.25398</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>60012 ESTHER ANGULO DE PASQUEL</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-3.75376</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.25597999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>362</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.75376</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.25598</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>60050 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-3.74958</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-73.24709</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1721</v>
-      </c>
-      <c r="J20" t="n">
-        <v>79</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-3.74958</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-73.24709</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>60053 GRAL. AUGUSTO FREYRE GARCIA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-3.73885</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-73.24476</v>
-      </c>
-      <c r="I21" t="n">
-        <v>677</v>
-      </c>
-      <c r="J21" t="n">
-        <v>39</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-3.73885</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-73.24476</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>60054 JOSE SILFO ALVAN DEL CASTILLO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-3.74596</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-73.25194999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>728</v>
-      </c>
-      <c r="J22" t="n">
-        <v>37</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-3.74596</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-73.25195</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>60055 SERAFIN FILOMENO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-3.74301</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-73.24826</v>
-      </c>
-      <c r="I23" t="n">
-        <v>365</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-3.74301</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-73.24826</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>60060 CESAR CALVO DE ARAUJO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-3.74064</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-73.25753</v>
-      </c>
-      <c r="I24" t="n">
-        <v>296</v>
-      </c>
-      <c r="J24" t="n">
-        <v>21</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-3.74064</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-73.25753</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>60188 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-3.73186</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-73.26504</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1981</v>
-      </c>
-      <c r="J25" t="n">
-        <v>90</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-3.73186</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-73.26504</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>60747 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-3.73443</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-73.25063</v>
-      </c>
-      <c r="I26" t="n">
-        <v>828</v>
-      </c>
-      <c r="J26" t="n">
-        <v>36</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-3.73443</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-73.25063</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>60793</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-3.753423</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-73.267758</v>
-      </c>
-      <c r="I27" t="n">
-        <v>846</v>
-      </c>
-      <c r="J27" t="n">
-        <v>52</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-3.753423</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-73.267758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>60826 ELEODORO BUSTAMANTE LOPEZ</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-3.745</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-73.26423</v>
-      </c>
-      <c r="I28" t="n">
-        <v>432</v>
-      </c>
-      <c r="J28" t="n">
-        <v>22</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-3.745</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-73.26423</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>60946 MARISCAL OSCAR R. BENAVIDES / MARISCAL OSCAR R. BENAVIDES</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-3.74848</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-73.25939</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3954</v>
-      </c>
-      <c r="J29" t="n">
-        <v>207</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-3.74848</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-73.25939</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>61001 CLUB DE LEONES</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-3.74272</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-73.25225</v>
-      </c>
-      <c r="I30" t="n">
-        <v>982</v>
-      </c>
-      <c r="J30" t="n">
-        <v>45</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-3.74272</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-73.25225</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>61003 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-3.75747</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-73.24894999999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>390</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-3.75747</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-73.24895</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>61004 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-3.76329</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-73.25608</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1747</v>
-      </c>
-      <c r="J32" t="n">
-        <v>83</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-3.76329</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-73.25608</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>61008 JUAN BAUTISTA MORI ROSALES</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-3.75565</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-73.25075</v>
-      </c>
-      <c r="I33" t="n">
-        <v>237</v>
-      </c>
-      <c r="J33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-3.75565</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-73.25075</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>61010 FERNANDO LORES TENAZOA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-3.74906</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-73.24279</v>
-      </c>
-      <c r="I34" t="n">
-        <v>891</v>
-      </c>
-      <c r="J34" t="n">
-        <v>52</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-3.74906</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-73.24279</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>61014 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-3.74279</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-73.24571</v>
-      </c>
-      <c r="I35" t="n">
-        <v>379</v>
-      </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-3.74279</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-73.24571</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>601050 / 601050 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-3.75324</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-73.27345</v>
-      </c>
-      <c r="I36" t="n">
-        <v>984</v>
-      </c>
-      <c r="J36" t="n">
-        <v>51</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-3.75324</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-73.27345</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>601066 MONITOR HUASCAR</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-3.73561</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-73.2569</v>
-      </c>
-      <c r="I37" t="n">
-        <v>356</v>
-      </c>
-      <c r="J37" t="n">
-        <v>23</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-3.73561</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-73.2569</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>601555 TARAPACA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-3.76358</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-73.262</v>
-      </c>
-      <c r="I38" t="n">
-        <v>274</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-3.76358</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-73.262</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>6010156 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-3.747387</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-73.26339299999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>959</v>
-      </c>
-      <c r="J39" t="n">
-        <v>36</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-3.747387</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-73.263393</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-3.7502</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-73.24590000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1562</v>
-      </c>
-      <c r="J40" t="n">
-        <v>85</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-3.7502</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-73.2459</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>ROSA AGUSTINA DONAYRE DE MOREY</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-3.74257</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-73.25234</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2690</v>
-      </c>
-      <c r="J41" t="n">
-        <v>137</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-3.74257</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-73.25234</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>COAR LORETO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-3.74581</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-73.26311</v>
-      </c>
-      <c r="I42" t="n">
-        <v>252</v>
-      </c>
-      <c r="J42" t="n">
-        <v>32</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-3.74581</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-73.26311</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>MAYNAS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-3.73433</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-73.25175</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1755</v>
-      </c>
-      <c r="J43" t="n">
-        <v>85</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-3.73433</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-73.25175</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>CORONEL FAP FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-3.74405</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-73.26133</v>
-      </c>
-      <c r="I44" t="n">
-        <v>433</v>
-      </c>
-      <c r="J44" t="n">
-        <v>45</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-3.74405</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-73.26133</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-3.75254</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-73.26452</v>
-      </c>
-      <c r="I45" t="n">
-        <v>382</v>
-      </c>
-      <c r="J45" t="n">
-        <v>26</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-3.75254</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-73.26452</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>REMANENTE DE DIOS</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-3.74878</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-73.24872000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>363</v>
-      </c>
-      <c r="J46" t="n">
-        <v>24</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-3.74878</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-73.24872</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>NUESTRA SEÑORA DE LORETO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-3.74464</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-73.24446</v>
-      </c>
-      <c r="I47" t="n">
-        <v>796</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-3.74464</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-73.24446</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-3.75463</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-73.25020000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1199</v>
-      </c>
-      <c r="J48" t="n">
-        <v>70</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-3.75463</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-73.2502</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>AMAZONAS</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-3.74694</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-73.24657000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>563</v>
-      </c>
-      <c r="J49" t="n">
-        <v>32</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-3.74694</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-73.24657</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-3.75141</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-73.24956</v>
-      </c>
-      <c r="I50" t="n">
-        <v>491</v>
-      </c>
-      <c r="J50" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-3.75141</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-73.24956</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-3.73904</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-73.25073</v>
-      </c>
-      <c r="I51" t="n">
-        <v>346</v>
-      </c>
-      <c r="J51" t="n">
-        <v>23</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-3.73904</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-73.25073</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>BETANIA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-3.73687</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-73.24891</v>
-      </c>
-      <c r="I52" t="n">
-        <v>247</v>
-      </c>
-      <c r="J52" t="n">
-        <v>20</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-3.73687</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-73.24891</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>VIRGEN DE LORETO</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-3.7419</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-73.24146</v>
-      </c>
-      <c r="I53" t="n">
-        <v>857</v>
-      </c>
-      <c r="J53" t="n">
-        <v>46</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-3.7419</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-73.24146</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>60019 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-3.7525772929281</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-73.2576600701402</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1669</v>
-      </c>
-      <c r="J54" t="n">
-        <v>75</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-3.7525772929281</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-73.2576600701402</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-3.75141</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-73.24956</v>
-      </c>
-      <c r="I55" t="n">
-        <v>290</v>
-      </c>
-      <c r="J55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-3.75141</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-73.24956</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>KAIRO'S</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-3.76004</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-73.25339</v>
-      </c>
-      <c r="I56" t="n">
-        <v>418</v>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-3.76004</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-73.25339</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-3.72868</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-73.24514000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>638</v>
-      </c>
-      <c r="J57" t="n">
-        <v>28</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-3.72868</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-73.24514</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>60058 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-3.73251</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-73.24628</v>
-      </c>
-      <c r="I58" t="n">
-        <v>337</v>
-      </c>
-      <c r="J58" t="n">
-        <v>22</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-3.73251</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-73.24628</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>60059 ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-3.73211</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-73.24284</v>
-      </c>
-      <c r="I59" t="n">
-        <v>633</v>
-      </c>
-      <c r="J59" t="n">
-        <v>33</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-3.73211</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-73.24284</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>TENIENTE MANUEL CLAVERO MUGA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-3.731232</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-73.24912500000001</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1315</v>
-      </c>
-      <c r="J60" t="n">
-        <v>68</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-3.731232</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-73.249125</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>CESAR VALLEJO / COOPERATIVA CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-3.74448</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-73.25024999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1362</v>
-      </c>
-      <c r="J61" t="n">
-        <v>64</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-3.74448</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-73.25025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>CORPUS CHRISTI ENGLISH SCHOLL / CORPUS CHRISTI ENGLISH SCHOOL</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-3.74317</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-73.24454</v>
-      </c>
-      <c r="I62" t="n">
-        <v>319</v>
-      </c>
-      <c r="J62" t="n">
-        <v>22</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-3.74317</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-73.24454</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>157 VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-3.74305</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-73.24603</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J63" t="n">
-        <v>49</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-3.74305</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-73.24603</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-3.76196</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-73.25594</v>
-      </c>
-      <c r="I64" t="n">
-        <v>149</v>
-      </c>
-      <c r="J64" t="n">
-        <v>21</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-3.76196</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-73.25594</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>60793 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-3.752886</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-73.268625</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1292</v>
-      </c>
-      <c r="J65" t="n">
-        <v>63</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-3.752886</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-73.268625</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>LORETO</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-3.74523</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-73.26296000000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>852</v>
-      </c>
-      <c r="J66" t="n">
-        <v>45</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-3.74523</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-73.26296</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>HUELLITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-3.744</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-73.24941</v>
-      </c>
-      <c r="I67" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-3.744</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-73.24941</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,22 +4601,156 @@
           <t>ALELUYA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-3.759602</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-73.256471</v>
-      </c>
-      <c r="I68" t="n">
-        <v>234</v>
-      </c>
-      <c r="J68" t="n">
-        <v>15</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-3.759602</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-73.256471</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>160101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MAYNAS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IQUITOS</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>365189</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60023</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-3.75581</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-73.25882</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>160101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MAYNAS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>IQUITOS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>367980</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>EMANUEL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-3.7513766</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-73.2556141</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>364062</t>
+          <t>364137</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>162 LOS HONGUITOS</t>
+          <t>179 EL PILOTO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.74757</t>
+          <t>-3.75457</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.25349</t>
+          <t>-73.25263</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>364118</t>
+          <t>364279</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>172 ANGEL DE LA GUARDA</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.7415</t>
+          <t>-3.805688</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.257693</t>
+          <t>-73.34148</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,27 +625,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>364137</t>
+          <t>365113</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>179 EL PILOTO</t>
+          <t>60007 BRASIL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.75457</t>
+          <t>-3.74889</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.25263</t>
+          <t>-73.25398</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>364161</t>
+          <t>364745</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>312 GRILLITO</t>
+          <t>593 MIS GARABATOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.74532</t>
+          <t>-3.73247</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.26427</t>
+          <t>-73.26884</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>364175</t>
+          <t>364892</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>691 RAYITOS DE ESPERANZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.73593</t>
+          <t>-3.72995</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.24925</t>
+          <t>-73.2625</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>364279</t>
+          <t>366886</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>ROSA AGUSTINA DONAYRE DE MOREY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.805688</t>
+          <t>-3.74257</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.34148</t>
+          <t>-73.25234</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>364298</t>
+          <t>364477</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>476 LOS ARBOLITOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.75575</t>
+          <t>-3.74002</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.27121</t>
+          <t>-73.24925</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>364477</t>
+          <t>364118</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>476 LOS ARBOLITOS</t>
+          <t>172 ANGEL DE LA GUARDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.74002</t>
+          <t>-3.7415</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.24925</t>
+          <t>-73.257693</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>364745</t>
+          <t>364161</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>593 MIS GARABATOS</t>
+          <t>312 GRILLITO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.73247</t>
+          <t>-3.74532</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.26884</t>
+          <t>-73.26427</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>364892</t>
+          <t>365028</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>691 RAYITOS DE ESPERANZA</t>
+          <t>717</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.72995</t>
+          <t>-3.7512</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.2625</t>
+          <t>-73.25926</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>365028</t>
+          <t>368003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>KAIRO'S</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.7512</t>
+          <t>-3.76004</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.25926</t>
+          <t>-73.25339</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>365052</t>
+          <t>906941</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>601374 SIMON BOLIVAR / 754</t>
+          <t>ALELUYA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.777049</t>
+          <t>-3.759602</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.302092</t>
+          <t>-73.256471</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>365066</t>
+          <t>365085</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60756 CLAVERITO / 756 CLAVERITO</t>
+          <t>60001 MENELEO MEZA LOPEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.7327</t>
+          <t>-3.75599</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.24986</t>
+          <t>-73.24995</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>365085</t>
+          <t>365090</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60001 MENELEO MEZA LOPEZ</t>
+          <t>60002 ANTONIO ALVAREZ VASQUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.75599</t>
+          <t>-3.756</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.24995</t>
+          <t>-73.253284</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>365090</t>
+          <t>365146</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60002 ANTONIO ALVAREZ VASQUEZ</t>
+          <t>60012 ESTHER ANGULO DE PASQUEL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.756</t>
+          <t>-3.75376</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.253284</t>
+          <t>-73.25598</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>365108</t>
+          <t>366061</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60005 MARIA PARADO DE BELLIDO</t>
+          <t>61008 JUAN BAUTISTA MORI ROSALES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.76083</t>
+          <t>-3.75565</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.25421</t>
+          <t>-73.25075</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>365113</t>
+          <t>366645</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60007 BRASIL</t>
+          <t>601555 TARAPACA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.74889</t>
+          <t>-3.76358</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.25398</t>
+          <t>-73.262</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>365146</t>
+          <t>364175</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60012 ESTHER ANGULO DE PASQUEL</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.75376</t>
+          <t>-3.73593</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.25598</t>
+          <t>-73.24925</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>365306</t>
+          <t>366080</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60050 REPUBLICA DE VENEZUELA</t>
+          <t>61014 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.74958</t>
+          <t>-3.74279</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.24709</t>
+          <t>-73.24571</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>365311</t>
+          <t>843010</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60053 GRAL. AUGUSTO FREYRE GARCIA</t>
+          <t>HUELLITAS DE AMOR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.73885</t>
+          <t>-3.744</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-73.24476</t>
+          <t>-73.24941</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>365325</t>
+          <t>364298</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60054 JOSE SILFO ALVAN DEL CASTILLO</t>
+          <t>342</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.74596</t>
+          <t>-3.75575</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-73.25195</t>
+          <t>-73.27121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>365330</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60055 SERAFIN FILOMENO</t>
+          <t>601374 SIMON BOLIVAR / 754</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.74301</t>
+          <t>-3.777049</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-73.24826</t>
+          <t>-73.302092</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>365354</t>
+          <t>367664</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60060 CESAR CALVO DE ARAUJO</t>
+          <t>BETANIA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.74064</t>
+          <t>-3.73687</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-73.25753</t>
+          <t>-73.24891</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>365698</t>
+          <t>365900</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60188 SIMON BOLIVAR</t>
+          <t>60946 MARISCAL OSCAR R. BENAVIDES / MARISCAL OSCAR R. BENAVIDES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.73186</t>
+          <t>-3.74848</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-73.26504</t>
+          <t>-73.25939</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>365778</t>
+          <t>365354</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60747 DIVINO MAESTRO</t>
+          <t>60060 CESAR CALVO DE ARAUJO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.73443</t>
+          <t>-3.74064</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-73.25063</t>
+          <t>-73.25753</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>365801</t>
+          <t>740597</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.753423</t>
+          <t>-3.76196</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-73.267758</t>
+          <t>-73.25594</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>365900</t>
+          <t>366023</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60946 MARISCAL OSCAR R. BENAVIDES / MARISCAL OSCAR R. BENAVIDES</t>
+          <t>61003 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.74848</t>
+          <t>-3.75747</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-73.25939</t>
+          <t>-73.24895</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>366004</t>
+          <t>373392</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61001 CLUB DE LEONES</t>
+          <t>60058 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.74272</t>
+          <t>-3.73251</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-73.25225</t>
+          <t>-73.24628</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,27 +2299,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>366023</t>
+          <t>539910</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61003 MARIA AUXILIADORA</t>
+          <t>CORPUS CHRISTI ENGLISH SCHOLL / CORPUS CHRISTI ENGLISH SCHOOL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.75747</t>
+          <t>-3.74317</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-73.24895</t>
+          <t>-73.24454</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>366037</t>
+          <t>366136</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61004 JUAN PABLO II</t>
+          <t>601066 MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.76329</t>
+          <t>-3.73561</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-73.25608</t>
+          <t>-73.2569</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,42 +2423,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>366061</t>
+          <t>367659</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61008 JUAN BAUTISTA MORI ROSALES</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.75565</t>
+          <t>-3.73904</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-73.25075</t>
+          <t>-73.25073</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>366075</t>
+          <t>367353</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61010 FERNANDO LORES TENAZOA</t>
+          <t>REMANENTE DE DIOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.74906</t>
+          <t>-3.74878</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-73.24279</t>
+          <t>-73.24872</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>363</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>366080</t>
+          <t>365330</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61014 HORACIO ZEVALLOS GAMEZ</t>
+          <t>60055 SERAFIN FILOMENO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.74279</t>
+          <t>-3.74301</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-73.24571</t>
+          <t>-73.24826</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>366117</t>
+          <t>367621</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>601050 / 601050 MICAELA BASTIDAS</t>
+          <t>ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.75324</t>
+          <t>-3.75141</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-73.27345</t>
+          <t>-73.24956</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>366136</t>
+          <t>367975</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>601066 MONITOR HUASCAR</t>
+          <t>ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.73561</t>
+          <t>-3.75141</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-73.2569</t>
+          <t>-73.24956</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>366645</t>
+          <t>367287</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>601555 TARAPACA</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.76358</t>
+          <t>-3.75254</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-73.262</t>
+          <t>-73.26452</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>366706</t>
+          <t>364062</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6010156 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>162 LOS HONGUITOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.747387</t>
+          <t>-3.74757</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-73.263393</t>
+          <t>-73.25349</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>366872</t>
+          <t>373052</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.7502</t>
+          <t>-3.72868</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-73.2459</t>
+          <t>-73.24514</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>366886</t>
+          <t>367485</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ROSA AGUSTINA DONAYRE DE MOREY</t>
+          <t>NUESTRA SEÑORA DE LORETO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.74257</t>
+          <t>-3.74464</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-73.25234</t>
+          <t>-73.24446</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>796</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>367070</t>
+          <t>367560</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MAYNAS</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.73433</t>
+          <t>-3.74694</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-73.25175</t>
+          <t>-73.24657</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>563</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>367268</t>
+          <t>373405</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CORONEL FAP FRANCISCO SECADA VIGNETTA</t>
+          <t>60059 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.74405</t>
+          <t>-3.73211</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-73.26133</t>
+          <t>-73.24284</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>633</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>367287</t>
+          <t>365778</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>60747 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.75254</t>
+          <t>-3.73443</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-73.26452</t>
+          <t>-73.25063</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>828</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>367353</t>
+          <t>366706</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>REMANENTE DE DIOS</t>
+          <t>6010156 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.74878</t>
+          <t>-3.747387</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-73.24872</t>
+          <t>-73.263393</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>959</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>367485</t>
+          <t>365325</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LORETO</t>
+          <t>60054 JOSE SILFO ALVAN DEL CASTILLO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.74464</t>
+          <t>-3.74596</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-73.24446</t>
+          <t>-73.25195</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>728</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>367541</t>
+          <t>365311</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>60053 GRAL. AUGUSTO FREYRE GARCIA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.75463</t>
+          <t>-3.73885</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-73.2502</t>
+          <t>-73.24476</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>677</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>367560</t>
+          <t>366004</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>61001 CLUB DE LEONES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.74694</t>
+          <t>-3.74272</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-73.24657</t>
+          <t>-73.25225</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>982</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>367621</t>
+          <t>367268</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ROSA DE AMERICA</t>
+          <t>CORONEL FAP FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.75141</t>
+          <t>-3.74405</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-73.24956</t>
+          <t>-73.26133</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>367659</t>
+          <t>813131</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.73904</t>
+          <t>-3.74523</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-73.25073</t>
+          <t>-73.26296</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>852</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>367664</t>
+          <t>367744</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BETANIA</t>
+          <t>VIRGEN DE LORETO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-3.73687</t>
+          <t>-3.7419</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-73.24891</t>
+          <t>-73.24146</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>857</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>367744</t>
+          <t>740385</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VIRGEN DE LORETO</t>
+          <t>157 VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-3.7419</t>
+          <t>-3.74305</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-73.24146</t>
+          <t>-73.24603</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>367937</t>
+          <t>366117</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60019 SAN MARTIN DE PORRES</t>
+          <t>601050 / 601050 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-3.7525772929281</t>
+          <t>-3.75324</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-73.2576600701402</t>
+          <t>-73.27345</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>984</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>367975</t>
+          <t>365108</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ROSA DE AMERICA</t>
+          <t>60005 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-3.75141</t>
+          <t>-3.76083</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-73.24956</t>
+          <t>-73.25421</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>869</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>368003</t>
+          <t>365801</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KAIRO'S</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-3.76004</t>
+          <t>-3.753423</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-73.25339</t>
+          <t>-73.267758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>846</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>373052</t>
+          <t>366075</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>61010 FERNANDO LORES TENAZOA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-3.72868</t>
+          <t>-3.74906</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-73.24514</t>
+          <t>-73.24279</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>891</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>373392</t>
+          <t>740639</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60058 SANTA ROSA DE LIMA</t>
+          <t>60793 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3.73251</t>
+          <t>-3.752886</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-73.24628</t>
+          <t>-73.268625</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>373405</t>
+          <t>527747</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60059 ANTONIO RAYMONDI</t>
+          <t>CESAR VALLEJO / COOPERATIVA CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.73211</t>
+          <t>-3.74448</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-73.24284</t>
+          <t>-73.25025</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4159,42 +4159,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>527747</t>
+          <t>367541</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO / COOPERATIVA CESAR VALLEJO</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-3.74448</t>
+          <t>-3.75463</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-73.25025</t>
+          <t>-73.2502</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>539910</t>
+          <t>367937</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CORPUS CHRISTI ENGLISH SCHOLL / CORPUS CHRISTI ENGLISH SCHOOL</t>
+          <t>60019 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-3.74317</t>
+          <t>-3.7525772929281</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-73.24454</t>
+          <t>-73.2576600701402</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>365306</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>157 VICTORIA BARCIA BONIFFATTI</t>
+          <t>60050 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-3.74305</t>
+          <t>-3.74958</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-73.24603</t>
+          <t>-73.24709</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>740597</t>
+          <t>365066</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>60756 CLAVERITO / 756 CLAVERITO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-3.76196</t>
+          <t>-3.7327</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-73.25594</t>
+          <t>-73.24986</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>740639</t>
+          <t>366037</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60793 TUPAC AMARU</t>
+          <t>61004 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-3.752886</t>
+          <t>-3.76329</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-73.268625</t>
+          <t>-73.25608</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>813131</t>
+          <t>366872</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-3.74523</t>
+          <t>-3.7502</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-73.26296</t>
+          <t>-73.2459</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>843010</t>
+          <t>367070</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HUELLITAS DE AMOR</t>
+          <t>MAYNAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-3.744</t>
+          <t>-3.73433</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-73.24941</t>
+          <t>-73.25175</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>906941</t>
+          <t>365698</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ALELUYA</t>
+          <t>60188 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-3.759602</t>
+          <t>-3.73186</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-73.256471</t>
+          <t>-73.26504</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>364137</t>
+          <t>906941</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>179 EL PILOTO</t>
+          <t>ALELUYA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.75457</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.25263</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-3.759602</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.256471</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>364279</t>
+          <t>843010</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>HUELLITAS DE AMOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.805688</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.34148</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-3.744</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.24941</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>365113</t>
+          <t>813131</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60007 BRASIL</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.74889</t>
+          <t>852</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.25398</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-3.74523</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.26296</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>364745</t>
+          <t>740639</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>593 MIS GARABATOS</t>
+          <t>60793 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.73247</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.26884</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-3.752886</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.268625</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>364892</t>
+          <t>740597</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>691 RAYITOS DE ESPERANZA</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.72995</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.2625</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-3.76196</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-73.25594</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>366886</t>
+          <t>740385</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ROSA AGUSTINA DONAYRE DE MOREY</t>
+          <t>157 VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.74257</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.25234</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>-3.74305</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>-73.24603</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>364477</t>
+          <t>539910</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>476 LOS ARBOLITOS</t>
+          <t>CORPUS CHRISTI ENGLISH SCHOLL / CORPUS CHRISTI ENGLISH SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.74002</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.24925</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-3.74317</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-73.24454</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>364118</t>
+          <t>527747</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>172 ANGEL DE LA GUARDA</t>
+          <t>CESAR VALLEJO / COOPERATIVA CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.7415</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.257693</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-3.74448</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.25025</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>364161</t>
+          <t>374056</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>312 GRILLITO</t>
+          <t>TENIENTE MANUEL CLAVERO MUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.74532</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.26427</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-3.731232</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.249125</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>365028</t>
+          <t>373405</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>60059 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.7512</t>
+          <t>633</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.25926</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-3.73211</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.24284</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>368003</t>
+          <t>373392</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KAIRO'S</t>
+          <t>60058 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.76004</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.25339</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-3.73251</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.24628</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>906941</t>
+          <t>373052</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALELUYA</t>
+          <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.759602</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.256471</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-3.72868</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.24514</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>365085</t>
+          <t>368003</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60001 MENELEO MEZA LOPEZ</t>
+          <t>KAIRO'S</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.75599</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.24995</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-3.76004</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.25339</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>365090</t>
+          <t>367980</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60002 ANTONIO ALVAREZ VASQUEZ</t>
+          <t>EMANUEL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.756</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.253284</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-3.7513766</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.2556141</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>365146</t>
+          <t>367975</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60012 ESTHER ANGULO DE PASQUEL</t>
+          <t>ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.75376</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.25598</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-3.75141</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.24956</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>366061</t>
+          <t>367937</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61008 JUAN BAUTISTA MORI ROSALES</t>
+          <t>60019 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.75565</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.25075</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-3.7525772929281</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.2576600701402</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>366645</t>
+          <t>367744</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>601555 TARAPACA</t>
+          <t>VIRGEN DE LORETO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.76358</t>
+          <t>857</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.262</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-3.7419</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.24146</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>364175</t>
+          <t>367664</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>BETANIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.73593</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.24925</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-3.73687</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.24891</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>366080</t>
+          <t>367659</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61014 HORACIO ZEVALLOS GAMEZ</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.74279</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.24571</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-3.73904</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.25073</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>843010</t>
+          <t>367621</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HUELLITAS DE AMOR</t>
+          <t>ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.744</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-73.24941</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-3.75141</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-73.24956</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>364298</t>
+          <t>367560</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.75575</t>
+          <t>563</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-73.27121</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>-3.74694</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.24657</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,42 +1803,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>365052</t>
+          <t>367541</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>601374 SIMON BOLIVAR / 754</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.777049</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-73.302092</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-3.75463</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.2502</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>367664</t>
+          <t>367485</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BETANIA</t>
+          <t>NUESTRA SEÑORA DE LORETO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.73687</t>
+          <t>796</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-73.24891</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-3.74464</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.24446</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,42 +1927,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>365900</t>
+          <t>367353</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60946 MARISCAL OSCAR R. BENAVIDES / MARISCAL OSCAR R. BENAVIDES</t>
+          <t>REMANENTE DE DIOS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.74848</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-73.25939</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>-3.74878</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-73.24872</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>365354</t>
+          <t>367287</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60060 CESAR CALVO DE ARAUJO</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.74064</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-73.25753</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-3.75254</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-73.26452</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>740597</t>
+          <t>367268</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>CORONEL FAP FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.76196</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-73.25594</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>-3.74405</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-73.26133</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>365820</t>
+          <t>367070</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60826 ELEODORO BUSTAMANTE LOPEZ</t>
+          <t>MAYNAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.745</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-73.26423</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-3.73433</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.25175</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>366023</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61003 MARIA AUXILIADORA</t>
+          <t>COAR LORETO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.75747</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-73.24895</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-3.74581</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.26311</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>373392</t>
+          <t>366886</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60058 SANTA ROSA DE LIMA</t>
+          <t>ROSA AGUSTINA DONAYRE DE MOREY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.73251</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-73.24628</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-3.74257</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.25234</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>539910</t>
+          <t>366872</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CORPUS CHRISTI ENGLISH SCHOLL / CORPUS CHRISTI ENGLISH SCHOOL</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.74317</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-73.24454</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-3.7502</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.2459</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>366136</t>
+          <t>366706</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>601066 MONITOR HUASCAR</t>
+          <t>6010156 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.73561</t>
+          <t>959</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-73.2569</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-3.747387</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.263393</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>367659</t>
+          <t>366645</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>601555 TARAPACA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.73904</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-73.25073</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-3.76358</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.262</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>367353</t>
+          <t>366136</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>REMANENTE DE DIOS</t>
+          <t>601066 MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.74878</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-73.24872</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>-3.73561</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-73.2569</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>365330</t>
+          <t>366117</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60055 SERAFIN FILOMENO</t>
+          <t>601050 / 601050 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.74301</t>
+          <t>984</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-73.24826</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-3.75324</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-73.27345</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>367621</t>
+          <t>366080</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ROSA DE AMERICA</t>
+          <t>61014 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.75141</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-73.24956</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-3.74279</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-73.24571</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>367975</t>
+          <t>366075</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ROSA DE AMERICA</t>
+          <t>61010 FERNANDO LORES TENAZOA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.75141</t>
+          <t>891</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-73.24956</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-3.74906</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-73.24279</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,42 +2733,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>367287</t>
+          <t>366061</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>61008 JUAN BAUTISTA MORI ROSALES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.75254</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-73.26452</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>-3.75565</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-73.25075</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>364062</t>
+          <t>366037</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>162 LOS HONGUITOS</t>
+          <t>61004 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.74757</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-73.25349</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-3.76329</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-73.25608</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>373052</t>
+          <t>366023</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>61003 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.72868</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-73.24514</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-3.75747</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-73.24895</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>367485</t>
+          <t>366004</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LORETO</t>
+          <t>61001 CLUB DE LEONES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.74464</t>
+          <t>982</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-73.24446</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>-3.74272</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-73.25225</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,42 +2981,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>367051</t>
+          <t>365900</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>COAR LORETO</t>
+          <t>60946 MARISCAL OSCAR R. BENAVIDES / MARISCAL OSCAR R. BENAVIDES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.74581</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-73.26311</t>
+          <t>207</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-3.74848</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-73.25939</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>367560</t>
+          <t>365820</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>60826 ELEODORO BUSTAMANTE LOPEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.74694</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-73.24657</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>-3.745</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-73.26423</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>373405</t>
+          <t>365801</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60059 ANTONIO RAYMONDI</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.73211</t>
+          <t>846</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-73.24284</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>-3.753423</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-73.267758</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3177,22 +3177,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>-3.73443</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-73.25063</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>828</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>366706</t>
+          <t>365698</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6010156 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>60188 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.747387</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-73.263393</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>-3.73186</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-73.26504</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>365325</t>
+          <t>365354</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60054 JOSE SILFO ALVAN DEL CASTILLO</t>
+          <t>60060 CESAR CALVO DE ARAUJO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.74596</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-73.25195</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>-3.74064</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-73.25753</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>365311</t>
+          <t>365330</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60053 GRAL. AUGUSTO FREYRE GARCIA</t>
+          <t>60055 SERAFIN FILOMENO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.73885</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-73.24476</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>-3.74301</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-73.24826</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>366004</t>
+          <t>365325</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61001 CLUB DE LEONES</t>
+          <t>60054 JOSE SILFO ALVAN DEL CASTILLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.74272</t>
+          <t>728</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-73.25225</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>-3.74596</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-73.25195</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>367268</t>
+          <t>365311</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CORONEL FAP FRANCISCO SECADA VIGNETTA</t>
+          <t>60053 GRAL. AUGUSTO FREYRE GARCIA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.74405</t>
+          <t>677</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-73.26133</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-3.73885</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-73.24476</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>813131</t>
+          <t>365306</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>60050 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.74523</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-73.26296</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>-3.74958</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-73.24709</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>367744</t>
+          <t>365189</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VIRGEN DE LORETO</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-3.7419</t>
+          <t>188</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-73.24146</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>-3.75581</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-73.25882</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>365146</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>157 VICTORIA BARCIA BONIFFATTI</t>
+          <t>60012 ESTHER ANGULO DE PASQUEL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-3.74305</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-73.24603</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>-3.75376</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-73.25598</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>366117</t>
+          <t>365113</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>601050 / 601050 MICAELA BASTIDAS</t>
+          <t>60007 BRASIL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-3.75324</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-73.27345</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>-3.74889</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-73.25398</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3797,22 +3797,22 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>-3.76083</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-73.25421</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>365801</t>
+          <t>365090</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>60002 ANTONIO ALVAREZ VASQUEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-3.753423</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-73.267758</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>-3.756</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-73.253284</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>366075</t>
+          <t>365085</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61010 FERNANDO LORES TENAZOA</t>
+          <t>60001 MENELEO MEZA LOPEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-3.74906</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-73.24279</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>-3.75599</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-73.24995</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>740639</t>
+          <t>365066</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60793 TUPAC AMARU</t>
+          <t>60756 CLAVERITO / 756 CLAVERITO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3.752886</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-73.268625</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>-3.7327</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-73.24986</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>527747</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO / COOPERATIVA CESAR VALLEJO</t>
+          <t>601374 SIMON BOLIVAR / 754</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.74448</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-73.25025</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>-3.777049</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-73.302092</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>374056</t>
+          <t>365028</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TENIENTE MANUEL CLAVERO MUGA</t>
+          <t>717</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-3.731232</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-73.249125</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>-3.7512</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-73.25926</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,37 +4159,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>367541</t>
+          <t>364892</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>691 RAYITOS DE ESPERANZA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-3.75463</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-73.2502</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>-3.72995</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-73.2625</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>367937</t>
+          <t>364745</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60019 SAN MARTIN DE PORRES</t>
+          <t>593 MIS GARABATOS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-3.7525772929281</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-73.2576600701402</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>-3.73247</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-73.26884</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>365306</t>
+          <t>364477</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60050 REPUBLICA DE VENEZUELA</t>
+          <t>476 LOS ARBOLITOS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-3.74958</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-73.24709</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>-3.74002</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-73.24925</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,42 +4345,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>365066</t>
+          <t>364298</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60756 CLAVERITO / 756 CLAVERITO</t>
+          <t>342</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-3.7327</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-73.24986</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>-3.75575</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-73.27121</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>366037</t>
+          <t>364279</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61004 JUAN PABLO II</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-3.76329</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-73.25608</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>-3.805688</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-73.34148</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>366872</t>
+          <t>364175</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-3.7502</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-73.2459</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>-3.73593</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-73.24925</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>367070</t>
+          <t>364161</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MAYNAS</t>
+          <t>312 GRILLITO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-3.73433</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-73.25175</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>-3.74532</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-73.26427</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>365698</t>
+          <t>364137</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60188 SIMON BOLIVAR</t>
+          <t>179 EL PILOTO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-3.73186</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-73.26504</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>-3.75457</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-73.25263</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>365189</t>
+          <t>364118</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60023</t>
+          <t>172 ANGEL DE LA GUARDA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-3.75581</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-73.25882</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>-3.7415</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-73.257693</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>367980</t>
+          <t>364062</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>EMANUEL</t>
+          <t>162 LOS HONGUITOS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-3.7513766</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-73.2556141</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-3.74757</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-73.25349</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-IQUITOS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
